--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_9.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_9.xlsx
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PerfectionismRating</t>
+          <t>Coffee?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.7232319662471026</v>
+        <v>-2.187163177029748</v>
       </c>
       <c r="C2">
-        <v>0.7756192656649703</v>
+        <v>1.145157360641587</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-1.787033476260903</v>
+        <v>-1.521564490147865</v>
       </c>
       <c r="C3">
-        <v>0.9543099142229489</v>
+        <v>0.8289023354506342</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-1.815689931620351</v>
+        <v>-2.642756753679983</v>
       </c>
       <c r="C4">
-        <v>1.062943617958889</v>
+        <v>1.260905357660687</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9148060186526616</v>
+        <v>0.1679063280564683</v>
       </c>
       <c r="C5">
-        <v>-1.404797122206734</v>
+        <v>-0.4883968628405458</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.9882069792549837</v>
+        <v>0.9920643702234158</v>
       </c>
       <c r="C6">
-        <v>-0.6341395706049391</v>
+        <v>-0.6916746474694162</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.083410770226261</v>
+        <v>-0.3440169245453542</v>
       </c>
       <c r="C7">
-        <v>0.7459290561440587</v>
+        <v>-1.772474037587822</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3815158538119947</v>
+        <v>1.404567643701379</v>
       </c>
       <c r="C8">
-        <v>-0.1978710270918319</v>
+        <v>0.5879940264839363</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-2.319838604071822</v>
+        <v>1.998065986186252</v>
       </c>
       <c r="C9">
-        <v>1.318051054587604</v>
+        <v>-2.090581951861285</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.5686746205857499</v>
+        <v>1.019800180238125</v>
       </c>
       <c r="C10">
-        <v>0.9859659607364161</v>
+        <v>-0.5575529303598428</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.120698737477376</v>
+        <v>1.179954697049905</v>
       </c>
       <c r="C11">
-        <v>-1.23251354021185</v>
+        <v>-0.6806666976379395</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.3632205771995946</v>
+        <v>-0.3544418757797936</v>
       </c>
       <c r="C12">
-        <v>0.3937988053431316</v>
+        <v>-0.5854146756918097</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-1.767459237356495</v>
+        <v>0.3076303511423692</v>
       </c>
       <c r="C13">
-        <v>1.750045944767083</v>
+        <v>-0.9338767583093431</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.2983297735171414</v>
+        <v>1.875755810691885</v>
       </c>
       <c r="C14">
-        <v>1.487352995501899</v>
+        <v>0.5341223338576326</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.8431370872809685</v>
+        <v>0.8864692828289461</v>
       </c>
       <c r="C15">
-        <v>0.5092088960330099</v>
+        <v>0.6703984844016815</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.076866839874256</v>
+        <v>-0.2422755775348787</v>
       </c>
       <c r="C16">
-        <v>-0.4457624380585029</v>
+        <v>1.279915696396961</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1049721948590042</v>
+        <v>-1.137799460288955</v>
       </c>
       <c r="C17">
-        <v>0.0536936946030395</v>
+        <v>0.7969186813612836</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.117199170725262</v>
+        <v>-0.3572255345721849</v>
       </c>
       <c r="C18">
-        <v>0.9396465991231264</v>
+        <v>0.04311890589920196</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.5425122561293176</v>
+        <v>1.855900972614582</v>
       </c>
       <c r="C19">
-        <v>0.4249629238889404</v>
+        <v>-1.659757666062273</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.8497613807991727</v>
+        <v>-0.4262936571913537</v>
       </c>
       <c r="C20">
-        <v>1.241882372385562</v>
+        <v>0.1339492219585117</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-1.240731313714854</v>
+        <v>0.8081445821278732</v>
       </c>
       <c r="C21">
-        <v>0.6252830155013795</v>
+        <v>0.7221811993488776</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.495138188680295</v>
+        <v>-0.1884376163414705</v>
       </c>
       <c r="C22">
-        <v>-0.4228637253876759</v>
+        <v>-1.481614178686825</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.8034774664736792</v>
+        <v>-0.5710005465490372</v>
       </c>
       <c r="C23">
-        <v>-0.4654329229512099</v>
+        <v>-1.912860018764054</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.6977062220086693</v>
+        <v>0.5971423452923792</v>
       </c>
       <c r="C24">
-        <v>0.6768816077041724</v>
+        <v>0.02207966880214607</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.9900768213385608</v>
+        <v>0.7447257042910161</v>
       </c>
       <c r="C25">
-        <v>-0.4689184634984142</v>
+        <v>-0.9775848462462848</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.816532624593208</v>
+        <v>-2.402458664054925</v>
       </c>
       <c r="C26">
-        <v>1.285711323797249</v>
+        <v>0.3781329939812096</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.2137807114559279</v>
+        <v>-1.940946994750422</v>
       </c>
       <c r="C27">
-        <v>0.5713638952509207</v>
+        <v>0.05299322887039104</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.6046010111603856</v>
+        <v>0.5276689904013345</v>
       </c>
       <c r="C28">
-        <v>-0.4536224826325406</v>
+        <v>-1.744624341824218</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.4779019983836531</v>
+        <v>1.225629265926816</v>
       </c>
       <c r="C29">
-        <v>0.463335277194482</v>
+        <v>-1.296857081354156</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.4932704233723296</v>
+        <v>-0.0585598527249428</v>
       </c>
       <c r="C30">
-        <v>-1.04485688201254</v>
+        <v>-0.604211365305115</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.8787082620609289</v>
+        <v>0.02539976089185851</v>
       </c>
       <c r="C31">
-        <v>-1.781154874119068</v>
+        <v>-0.4391988817622003</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.3606239671695992</v>
+        <v>0.9458889646902472</v>
       </c>
       <c r="C32">
-        <v>0.07045640912156531</v>
+        <v>-1.359605597286743</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.2496940057696057</v>
+        <v>1.138397512895203</v>
       </c>
       <c r="C33">
-        <v>1.216616297057324</v>
+        <v>0.6137305298364106</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.6128280799392314</v>
+        <v>-1.003534199598925</v>
       </c>
       <c r="C34">
-        <v>0.7909265492887793</v>
+        <v>-0.3914433325255261</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.5971128947898012</v>
+        <v>-0.2388166925857885</v>
       </c>
       <c r="C35">
-        <v>-0.4344120728996214</v>
+        <v>0.5752523589871874</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.8813353255423261</v>
+        <v>-0.3486848443821439</v>
       </c>
       <c r="C36">
-        <v>1.497444831051945</v>
+        <v>-0.005264076450229582</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.7361853309067823</v>
+        <v>-0.2296608669349844</v>
       </c>
       <c r="C37">
-        <v>0.5152134182842739</v>
+        <v>0.9506181211474356</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.052918823487983</v>
+        <v>0.09109384991123176</v>
       </c>
       <c r="C38">
-        <v>0.1591445072262048</v>
+        <v>0.8197277127980003</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.07313588280231374</v>
+        <v>0.7552883398584164</v>
       </c>
       <c r="C39">
-        <v>0.1723586816510773</v>
+        <v>-2.30046219347641</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.220853411154399</v>
+        <v>0.6494662082019049</v>
       </c>
       <c r="C40">
-        <v>-0.2073466276972165</v>
+        <v>0.6520624434227684</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-1.08680396581779</v>
+        <v>-1.043047875573092</v>
       </c>
       <c r="C41">
-        <v>-0.4354318325549946</v>
+        <v>2.385813854432381</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.3791859530245538</v>
+        <v>0.9591045941179155</v>
       </c>
       <c r="C42">
-        <v>-0.5543040655447286</v>
+        <v>-0.2241984429119402</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.663880073192997</v>
+        <v>0.03453835812619612</v>
       </c>
       <c r="C43">
-        <v>0.266743936413869</v>
+        <v>-2.319363244758653</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.7815543832895484</v>
+        <v>-0.0448084838685066</v>
       </c>
       <c r="C44">
-        <v>0.9227435428260435</v>
+        <v>0.2562659805519236</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.254179777828361</v>
+        <v>2.467861863456356</v>
       </c>
       <c r="C45">
-        <v>1.294604899642407</v>
+        <v>-1.811910389308849</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.9041641204809734</v>
+        <v>0.02767724176143666</v>
       </c>
       <c r="C46">
-        <v>1.137695287382138</v>
+        <v>0.1110912222851722</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.7545813931423137</v>
+        <v>-0.3363853803826428</v>
       </c>
       <c r="C47">
-        <v>1.061817123957438</v>
+        <v>-1.252411160417192</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.057006551884468</v>
+        <v>0.5085964572459344</v>
       </c>
       <c r="C48">
-        <v>0.8380945200482675</v>
+        <v>-0.7167306429704415</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.4416257261356212</v>
+        <v>-0.03935914900147105</v>
       </c>
       <c r="C49">
-        <v>0.926536239709306</v>
+        <v>1.642030382294321</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.4828994742306764</v>
+        <v>2.416057368285303</v>
       </c>
       <c r="C50">
-        <v>-1.04745174900741</v>
+        <v>-1.010100207069953</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.5541313694737505</v>
+        <v>1.121374739274269</v>
       </c>
       <c r="C51">
-        <v>-1.304791686731787</v>
+        <v>-0.5758087151354573</v>
       </c>
     </row>
   </sheetData>
